--- a/ket_qua_C.xlsx
+++ b/ket_qua_C.xlsx
@@ -509,7 +509,7 @@
         <v>84</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.00588</v>
+        <v>0.000498</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>7</v>
@@ -536,7 +536,7 @@
         <v>146</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.001823</v>
+        <v>0.0007159999999999999</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>8</v>
@@ -563,7 +563,7 @@
         <v>230</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.000914</v>
+        <v>0.001059</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>9</v>
@@ -590,7 +590,7 @@
         <v>306</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.002543</v>
+        <v>0.001186</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>10</v>
@@ -617,7 +617,7 @@
         <v>392</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.001545</v>
+        <v>0.007273</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>11</v>
@@ -644,7 +644,7 @@
         <v>488</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.003098</v>
+        <v>0.001956</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>12</v>
@@ -671,7 +671,7 @@
         <v>594</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.003941</v>
+        <v>0.003057</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>13</v>
@@ -698,7 +698,7 @@
         <v>710</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.0035</v>
+        <v>0.010846</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>14</v>
@@ -725,7 +725,7 @@
         <v>836</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.003361</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>15</v>
@@ -752,7 +752,7 @@
         <v>972</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.009011999999999999</v>
+        <v>0.008513</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>16</v>
@@ -779,7 +779,7 @@
         <v>1118</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.006263</v>
+        <v>0.00457</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>17</v>
@@ -806,7 +806,7 @@
         <v>1274</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.003001</v>
+        <v>0.007069</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>18</v>
@@ -833,7 +833,7 @@
         <v>1440</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.003973</v>
+        <v>0.006409</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>19</v>
@@ -860,7 +860,7 @@
         <v>1616</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.005388</v>
+        <v>0.00958</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>20</v>
@@ -887,7 +887,7 @@
         <v>1802</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.010215</v>
+        <v>0.026286</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>21</v>
@@ -914,7 +914,7 @@
         <v>1998</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.018295</v>
+        <v>0.006765</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>22</v>
@@ -941,7 +941,7 @@
         <v>2204</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.020089</v>
+        <v>0.008593</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>23</v>
@@ -968,7 +968,7 @@
         <v>2420</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.015582</v>
+        <v>0.017628</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>24</v>
@@ -995,7 +995,7 @@
         <v>2646</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.022177</v>
+        <v>0.015072</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>25</v>
@@ -1022,7 +1022,7 @@
         <v>2882</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.011884</v>
+        <v>0.024641</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>26</v>
@@ -1049,7 +1049,7 @@
         <v>3128</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.013236</v>
+        <v>0.018221</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>27</v>
@@ -1076,7 +1076,7 @@
         <v>3384</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.011241</v>
+        <v>0.015171</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>28</v>
@@ -1103,7 +1103,7 @@
         <v>3650</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.01088</v>
+        <v>0.021666</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>29</v>
@@ -1130,7 +1130,7 @@
         <v>3926</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.01295</v>
+        <v>0.023145</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>30</v>
@@ -1157,7 +1157,7 @@
         <v>4212</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.01413</v>
+        <v>0.023012</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>31</v>
@@ -1184,7 +1184,7 @@
         <v>4508</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.021609</v>
+        <v>0.025426</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>32</v>
@@ -1211,7 +1211,7 @@
         <v>4814</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.01884</v>
+        <v>0.021754</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>33</v>
@@ -1238,7 +1238,7 @@
         <v>5130</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.025881</v>
+        <v>0.024871</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>34</v>
@@ -1265,7 +1265,7 @@
         <v>5456</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.020038</v>
+        <v>0.029825</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>35</v>
@@ -1292,7 +1292,7 @@
         <v>5792</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.017697</v>
+        <v>0.045927</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>36</v>
@@ -1319,7 +1319,7 @@
         <v>6138</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.021522</v>
+        <v>0.05272</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>37</v>
@@ -1346,7 +1346,7 @@
         <v>6494</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.018075</v>
+        <v>0.037502</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>38</v>
@@ -1373,7 +1373,7 @@
         <v>6860</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.022084</v>
+        <v>0.036815</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>39</v>
@@ -1400,7 +1400,7 @@
         <v>7236</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.021715</v>
+        <v>0.064988</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>40</v>
@@ -1427,7 +1427,7 @@
         <v>7622</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.02374</v>
+        <v>0.040569</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>41</v>
@@ -1454,7 +1454,7 @@
         <v>8018</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.021141</v>
+        <v>0.042433</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>42</v>
@@ -1481,7 +1481,7 @@
         <v>8424</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.02679</v>
+        <v>0.026302</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>43</v>
@@ -1508,7 +1508,7 @@
         <v>8840</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.029415</v>
+        <v>0.026338</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>44</v>
@@ -1535,7 +1535,7 @@
         <v>9266</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.039739</v>
+        <v>0.030087</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>45</v>
@@ -1562,7 +1562,7 @@
         <v>9702</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.024584</v>
+        <v>0.02723</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>46</v>
@@ -1589,7 +1589,7 @@
         <v>10148</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.027841</v>
+        <v>0.052838</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>47</v>
@@ -1616,7 +1616,7 @@
         <v>10604</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.032096</v>
+        <v>0.048859</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>48</v>
@@ -1643,7 +1643,7 @@
         <v>11070</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.031521</v>
+        <v>0.036089</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>49</v>
@@ -1670,7 +1670,7 @@
         <v>11546</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.123235</v>
+        <v>0.055997</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>50</v>
@@ -1697,7 +1697,7 @@
         <v>12032</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.047702</v>
+        <v>0.074199</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>51</v>
@@ -1724,7 +1724,7 @@
         <v>12528</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.096512</v>
+        <v>0.142562</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>52</v>
@@ -1751,7 +1751,7 @@
         <v>13034</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.047994</v>
+        <v>0.066951</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>53</v>
@@ -1778,7 +1778,7 @@
         <v>13550</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.044092</v>
+        <v>0.046864</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>54</v>
